--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583404</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104582840</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583451</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583448</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104582516</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104582518</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583377</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583402</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583406</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1715,6 +1765,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583443</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1816,6 +1871,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583470</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1917,6 +1977,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104582520</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104582521</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583436</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583457</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583458</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104583468</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88624809</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89009348</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2726,6 +2826,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89009349</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2828,6 +2933,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110644224</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2930,6 +3040,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110644223</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,8 +3142,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129045362</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3145,6 +3145,219 @@
       <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129045362</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136191981</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79444</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bjärnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>765364</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7153217</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136191981</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136191873</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bjärnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>765346</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7153211</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136191873</t>
         </is>
       </c>
     </row>
@@ -3173,6 +3386,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3153,7 +3153,7 @@
         <v>136191981</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3153,7 +3153,7 @@
         <v>136191981</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3153,7 +3153,7 @@
         <v>136191981</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3153,7 +3153,7 @@
         <v>136191981</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3153,7 +3153,7 @@
         <v>136191981</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3153,7 +3153,7 @@
         <v>136191981</v>
       </c>
       <c r="B25" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 456-2025 artfynd.xlsx
+++ b/artfynd/S 456-2025 artfynd.xlsx
@@ -3153,7 +3153,7 @@
         <v>136191981</v>
       </c>
       <c r="B25" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136191873</v>
       </c>
       <c r="B26" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
